--- a/REMS/wwwroot/reports/تقرير_قسم_المتابعة_20260820_000000.xlsx
+++ b/REMS/wwwroot/reports/تقرير_قسم_المتابعة_20260820_000000.xlsx
@@ -6,10 +6,12 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="تقرير_قسم_المتابعة" sheetId="2" r:id="rId2"/>
+    <x:sheet name="تقرير قسم المتابعة" sheetId="2" r:id="rId2"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">تقرير_قسم_المتابعة!$A$1:$AJ$2</x:definedName>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="0">'تقرير قسم المتابعة'!$A$1:$J$11</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'تقرير قسم المتابعة'!$A$4:$J$11</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles" localSheetId="0">'تقرير قسم المتابعة'!4:4</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -18,171 +20,133 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ملاحظات</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TaskDetails</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TaskType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClientOrProject</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AssignedEmployee</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Priority</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TotalItems</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CompletedItems</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CompletedDetails</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ExpectedDurationDays</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartDate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DueDate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CompletedDate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsDoneOrNot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>إنجاز</x:t>
-  </x:si>
-  <x:si>
-    <x:t>اسم الموظف</x:t>
-  </x:si>
-  <x:si>
-    <x:t>تاريخ الإدخال</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LastUpdatedDate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LastUpdatedBy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>الملف</x:t>
-  </x:si>
-  <x:si>
-    <x:t>المنطقة</x:t>
-  </x:si>
-  <x:si>
-    <x:t>المحافظة</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Coordinator</x:t>
-  </x:si>
-  <x:si>
-    <x:t>تاريخ العمل</x:t>
-  </x:si>
-  <x:si>
-    <x:t>اسم المتجر</x:t>
-  </x:si>
-  <x:si>
-    <x:t>نوع المتجر</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Address</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>توقيع العقد</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ContractFileName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ContractDate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AllTasksDone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>عدد المنتجات</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RemainingItems</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ProgressPercentage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
+    <x:t>◆  REMS  |  تقرير قسم المتابعة</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEMS • HEX STUDIO     |     تاريخ التقرير: 2026-08-20 00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</x:t>
+  </x:si>
+  <x:si>
+    <x:t>المهمة</x:t>
+  </x:si>
+  <x:si>
+    <x:t>النوع</x:t>
+  </x:si>
+  <x:si>
+    <x:t>العميل / المشروع</x:t>
+  </x:si>
+  <x:si>
+    <x:t>الموظف</x:t>
+  </x:si>
+  <x:si>
+    <x:t>الأولوية</x:t>
+  </x:si>
+  <x:si>
+    <x:t>التقدم</x:t>
+  </x:si>
+  <x:si>
+    <x:t>المنجز</x:t>
+  </x:si>
+  <x:si>
+    <x:t>المتبقي</x:t>
+  </x:si>
+  <x:si>
+    <x:t>الحالة</x:t>
+  </x:si>
+  <x:si>
+    <x:t>التسليم</x:t>
+  </x:si>
+  <x:si>
+    <x:t>نمس</x:t>
+  </x:si>
+  <x:si>
+    <x:t>تسويق</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ينةيس</x:t>
+  </x:si>
+  <x:si>
+    <x:t>فتون</x:t>
+  </x:si>
+  <x:si>
+    <x:t>متوسطة</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4 / 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>قيد التنفيذ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slkg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sklg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>هادي نعسان</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25 / 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>تعديل رييل</x:t>
+  </x:si>
+  <x:si>
+    <x:t>تصميم</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rems</x:t>
+  </x:si>
+  <x:si>
+    <x:t>حيدره ابو حمره</x:t>
+  </x:si>
+  <x:si>
+    <x:t>354 / 6584</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>عاجلة</x:t>
+  </x:si>
+  <x:si>
+    <x:t>اوك</x:t>
+  </x:si>
+  <x:si>
+    <x:t>عالية</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4 / 80</x:t>
   </x:si>
   <x:si>
     <x:t>تصوير مالمو</x:t>
   </x:si>
   <x:si>
-    <x:t>تصوير المنتجات النقص و تعديلها</x:t>
-  </x:si>
-  <x:si>
     <x:t>أخرى</x:t>
   </x:si>
   <x:si>
     <x:t>مالمو</x:t>
   </x:si>
   <x:si>
-    <x:t>حيدره ابو حمره</x:t>
-  </x:si>
-  <x:si>
-    <x:t>عاجلة</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>تم التصوير</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>قيد التنفيذ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>لا</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/Files/2026-08-20_19-58-13_e609437d-f479-45f5-93b0-9a0339f83af4.jpeg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>images.jpeg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50</x:t>
+    <x:t>1 / 2</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="164" formatCode="yyyy-MM-dd HH:mm"/>
+    <x:numFmt numFmtId="164" formatCode="0%"/>
+    <x:numFmt numFmtId="165" formatCode="yyyy-MM-dd"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="10">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -193,16 +157,69 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
+      <x:sz val="20"/>
+      <x:color rgb="FFF8FAFC"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
-      <x:u val="single"/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="10"/>
+      <x:color rgb="FFA5B4FC"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="7"/>
+      <x:color rgb="FF6366F1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
-      <x:color theme="10"/>
+      <x:color rgb="FFF8FAFC"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="10"/>
+      <x:color rgb="FFF8FAFC"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="10"/>
+      <x:color rgb="FFF59E0B"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="10"/>
+      <x:color rgb="FF38BDF8"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="10"/>
+      <x:color rgb="FF6366F1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="10"/>
+      <x:color rgb="FFEF4444"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -216,11 +233,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F2F2"/>
+        <x:fgColor theme="1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="15">
     <x:border diagonalUp="0" diagonalDown="0">
       <x:left style="none">
         <x:color rgb="FF000000"/>
@@ -238,40 +255,449 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF6366F1"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF6366F1"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF6366F1"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF343758"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF6366F1"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF1D4ED8"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF343758"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF343758"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF6366F1"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF1D4ED8"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF343758"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF6366F1"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF1D4ED8"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF20233A"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF20233A"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF20233A"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF312E81"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="8" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="9" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="7" fillId="2" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="11" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="2" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="2" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="5" fillId="2" borderId="11" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="12" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="13" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="13" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="2" borderId="13" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="13" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="5" fillId="2" borderId="14" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -568,255 +994,331 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
+    <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AJ2"/>
+  <x:dimension ref="A1:J11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.996339" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="35.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.567768" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20.139196" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.853482" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12.710625" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18.139196" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18.996339" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.567768" style="0" customWidth="1"/>
-    <x:col min="12" max="13" width="15.710625" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="17.282054" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="7.424911" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="15.424911" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="15.710625" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="18.710625" style="0" customWidth="1"/>
-    <x:col min="20" max="20" width="16.853482" style="0" customWidth="1"/>
-    <x:col min="21" max="21" width="65.282054" style="0" customWidth="1"/>
-    <x:col min="22" max="22" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="23" max="23" width="11.710625" style="0" customWidth="1"/>
-    <x:col min="24" max="24" width="13.996339" style="0" customWidth="1"/>
-    <x:col min="25" max="25" width="14.853482" style="0" customWidth="1"/>
-    <x:col min="26" max="26" width="13.424911" style="0" customWidth="1"/>
-    <x:col min="27" max="27" width="13.567768" style="0" customWidth="1"/>
-    <x:col min="28" max="28" width="10.424911" style="0" customWidth="1"/>
-    <x:col min="29" max="29" width="8.853482" style="0" customWidth="1"/>
-    <x:col min="30" max="30" width="65.282054" style="0" customWidth="1"/>
-    <x:col min="31" max="31" width="19.139196" style="0" customWidth="1"/>
-    <x:col min="32" max="32" width="15.282054" style="0" customWidth="1"/>
-    <x:col min="33" max="33" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="34" max="34" width="15.996339" style="0" customWidth="1"/>
-    <x:col min="35" max="35" width="17.710625" style="0" customWidth="1"/>
-    <x:col min="36" max="36" width="21.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="33.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="27.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17.710625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.710625" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="19.710625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:36">
+    <x:row r="1" spans="1:10" ht="42" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
+      <x:c r="J1" s="3"/>
+    </x:row>
+    <x:row r="2" spans="1:10" ht="25" customHeight="1">
+      <x:c r="A2" s="4" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="B2" s="5"/>
+      <x:c r="C2" s="5"/>
+      <x:c r="D2" s="5"/>
+      <x:c r="E2" s="5"/>
+      <x:c r="F2" s="5"/>
+      <x:c r="G2" s="5"/>
+      <x:c r="H2" s="5"/>
+      <x:c r="I2" s="5"/>
+      <x:c r="J2" s="6"/>
+    </x:row>
+    <x:row r="3" spans="1:10" ht="12" customHeight="1">
+      <x:c r="A3" s="7" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+      <x:c r="H3" s="8"/>
+      <x:c r="I3" s="8"/>
+      <x:c r="J3" s="9"/>
+    </x:row>
+    <x:row r="4" spans="1:10" ht="36" customHeight="1">
+      <x:c r="A4" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="B4" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="C4" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="D4" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="E4" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="F4" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="G4" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="H4" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
+      <x:c r="I4" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M1" s="1" t="s">
+      <x:c r="J4" s="12" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N1" s="1" t="s">
+    </x:row>
+    <x:row r="5" spans="1:10" ht="30" customHeight="1">
+      <x:c r="A5" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="O1" s="1" t="s">
+      <x:c r="B5" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="P1" s="1" t="s">
+      <x:c r="C5" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="Q1" s="1" t="s">
+      <x:c r="D5" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="R1" s="1" t="s">
+      <x:c r="E5" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="S1" s="1" t="s">
+      <x:c r="F5" s="16">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="T1" s="1" t="s">
+      <x:c r="H5" s="14">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I5" s="17" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="U1" s="1" t="s">
+      <x:c r="J5" s="18" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:10" ht="30" customHeight="1">
+      <x:c r="A6" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="V1" s="1" t="s">
+      <x:c r="B6" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="W1" s="1" t="s">
+      <x:c r="D6" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="X1" s="1" t="s">
+      <x:c r="E6" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F6" s="19">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="Y1" s="1" t="s">
+      <x:c r="H6" s="14">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J6" s="18" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:10" ht="30" customHeight="1">
+      <x:c r="A7" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="Z1" s="1" t="s">
+      <x:c r="B7" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="AA1" s="1" t="s">
+      <x:c r="C7" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="AB1" s="1" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="AC1" s="1" t="s">
+      <x:c r="E7" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" s="20">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="AD1" s="1" t="s">
+      <x:c r="H7" s="14">
+        <x:v>6230</x:v>
+      </x:c>
+      <x:c r="I7" s="17" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J7" s="21">
+        <x:v>46263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:10" ht="30" customHeight="1">
+      <x:c r="A8" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="AE1" s="1" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="AF1" s="1" t="s">
+      <x:c r="D8" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E8" s="22" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="AG1" s="1" t="s">
+      <x:c r="F8" s="16">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" s="17" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J8" s="18" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:10" ht="30" customHeight="1">
+      <x:c r="A9" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="AH1" s="1" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="AI1" s="1" t="s">
+      <x:c r="F9" s="20">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="AJ1" s="1" t="s">
+      <x:c r="H9" s="14">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:10" ht="30" customHeight="1">
+      <x:c r="A10" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="16">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H10" s="14">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="17" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J10" s="21">
+        <x:v>46259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:10" ht="30" customHeight="1">
+      <x:c r="A11" s="23" t="s">
         <x:v>35</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:36">
-      <x:c r="A2" s="2" t="s">
+      <x:c r="B11" s="24" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="s">
+      <x:c r="C11" s="24" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
+      <x:c r="D11" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="25" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F11" s="26">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="G11" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K2" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L2" s="3">
-        <x:v>46254</x:v>
-      </x:c>
-      <x:c r="M2" s="3">
+      <x:c r="H11" s="24">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I11" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J11" s="28">
         <x:v>46256</x:v>
-      </x:c>
-      <x:c r="N2" s="2" t="s"/>
-      <x:c r="O2" s="2" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="P2" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="Q2" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="R2" s="3">
-        <x:v>46254.8321054051</x:v>
-      </x:c>
-      <x:c r="S2" s="3">
-        <x:v>46254.8321054167</x:v>
-      </x:c>
-      <x:c r="T2" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="U2" s="4" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="V2" s="2" t="s"/>
-      <x:c r="W2" s="2" t="s"/>
-      <x:c r="X2" s="2" t="s"/>
-      <x:c r="Y2" s="2" t="s"/>
-      <x:c r="Z2" s="2" t="s"/>
-      <x:c r="AA2" s="2" t="s"/>
-      <x:c r="AB2" s="2" t="s"/>
-      <x:c r="AC2" s="2" t="s"/>
-      <x:c r="AD2" s="4" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AE2" s="2" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AF2" s="2" t="s"/>
-      <x:c r="AG2" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AH2" s="2" t="s"/>
-      <x:c r="AI2" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="AJ2" s="2" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:AJ2"/>
-  <x:hyperlinks>
-    <x:hyperlink ref="U2" location="تقرير_قسم_المتابعة!/Files/2026-08-20_19-58-13_e609437d-f479-45f5-93b0-9a0339f83af4.jpeg" display="/Files/2026-08-20_19-58-13_e609437d-f479-45f5-93b0-9a0339f83af4.jpeg"/>
-    <x:hyperlink ref="AD2" location="تقرير_قسم_المتابعة!/Files/2026-08-20_19-58-13_e609437d-f479-45f5-93b0-9a0339f83af4.jpeg" display="/Files/2026-08-20_19-58-13_e609437d-f479-45f5-93b0-9a0339f83af4.jpeg"/>
-  </x:hyperlinks>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:autoFilter ref="A4:J11"/>
+  <x:mergeCells count="3">
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A3:J3"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
+  <x:pageSetup paperSize="9" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader>&amp;LREMS&amp;CHEMS • HEX STUDIO&amp;R&amp;D</x:oddHeader>
+    <x:oddFooter>&amp;LREMS&amp;Cصفحة &amp;P من &amp;N&amp;R&amp;T</x:oddFooter>
+    <x:evenHeader>&amp;LREMS&amp;CHEMS • HEX STUDIO&amp;R&amp;D</x:evenHeader>
+    <x:evenFooter>&amp;LREMS&amp;Cصفحة &amp;P من &amp;N&amp;R&amp;T</x:evenFooter>
+    <x:firstHeader>&amp;LREMS&amp;CHEMS • HEX STUDIO&amp;R&amp;D</x:firstHeader>
+    <x:firstFooter>&amp;LREMS&amp;Cصفحة &amp;P من &amp;N&amp;R&amp;T</x:firstFooter>
+  </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>